--- a/docs/06-execution/execution-results.xlsx
+++ b/docs/06-execution/execution-results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +453,924 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC-AUTH-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TC-AUTH-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TC-AUTH-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC-AUTH-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC-AUTH-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC-AUTH-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC-AUTH-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC-DASH-001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC-DASH-002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC-DASH-003</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC-DASH-004</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC-PIM-001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC-PIM-002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC-PIM-003</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC-PIM-004</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC-PIM-005</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC-PIM-006</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC-PIM-007</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC-PIM-008</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC-PIM-009</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC-PIM-010</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC-PROF-001</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC-PROF-002</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC-PROF-003</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TC-PROF-004</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC-PROF-005</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TC-PROF-006</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-001</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-002</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-003</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-004</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-005</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-006</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-007</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-008</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-009</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-010</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-011</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-012</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-TIME-001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TC-TIME-002</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TC-TIME-003</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TC-TIME-004</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TC-TIME-005</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TC-REC-001</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TC-REC-002</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TC-REC-003</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TC-REC-004</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TC-REP-001</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TC-REP-002</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TC-REP-003</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TC-UI-001</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TC-COMP-001</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/06-execution/execution-results.xlsx
+++ b/docs/06-execution/execution-results.xlsx
@@ -461,14 +461,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Login page HTTP 200/title OrangeHRM with username+password+Login; qa_admin login lands /dashboard/index &lt;5s with admin user menu</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-AUTH-001-login-page.png + TC-AUTH-002-admin-dashboard.png</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -478,14 +493,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ESS login lands /dashboard/index with restricted 8-item nav (Leave/Time/My Info/Performance/Dashboard/Directory/Claim/Buzz); Admin+PIM+Recruitment+Maintenance absent. Expected text says "PIM/Leave visible" — PIM is correctly hidden for ESS; test-design wording needs correction, NOT an SUT defect. No BUG filed.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-AUTH-002-ess-dashboard.png; TEST-DESIGN issue flagged, Expected frozen per process</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -495,14 +525,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Wrong password rejected; stays on /auth/login with "Invalid credentials" toast; no session</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-AUTH-003-invalid-password.png</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -512,14 +557,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Unknown username rejected with generic "Invalid credentials" (same as wrong password — no account enumeration); stays on login, no session</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-AUTH-004-unknown-user.png</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -529,14 +589,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Empty username+password rejected inline with "Required" x2; stays on login, no session</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-AUTH-005-empty-credentials.png</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -546,14 +621,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Whitespace-only credentials treated as empty: "Required" x2 shown; stays on login, no session</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-AUTH-006-whitespace-credentials.png</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -563,14 +653,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Logout via user menu returns to /auth/login</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-AUTH-007-after-logout.png</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -580,14 +685,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Browser Back + direct /dashboard/index after logout both land on /auth/login; no authenticated content or action possible</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-AUTH-008-back-button.png + TC-DASH-004-direct-url-after-logout.png</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -597,14 +717,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Admin dashboard loads with 12-item nav (Admin/PIM/Leave/Time/Recruitment/My Info/Performance/Dashboard/Directory/Maintenance/Claim/Buzz); ESS dashboard loads with 8-item restricted nav</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-DASH-001-dashboard-load.png + TC-AUTH-002-*-dashboard.png</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -614,14 +749,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PIM/Leave/Time/Recruitment nav targets each land on matching module (h6 PIM/Leave/Time+Timesheets/Recruitment)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-DASH-002-nav-recruitment.png</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -634,11 +784,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -648,14 +793,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Unauthenticated /dashboard/index redirects to /auth/login; no dashboard content exposed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-DASH-004-direct-url-after-logout.png</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -665,14 +825,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Employee E2091 (PhaseNine Probe) saved and retrieved by ID search: 1 card E2091 | PhaseNine | Probe</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-PIM-001-created-E2091.png; synthetic record, disposable</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -682,14 +857,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Empty-required blocked inline ("Required" x2, stays on form); duplicate E2091 blocked ("Employee Id already exists", stays on form); ID search confirms still exactly 1 E2091 record — no silent save, no duplicate</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-PIM-002-empty-required.png + TC-PIM-002-duplicate-id.png</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -699,14 +889,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Assumed 50-char max is wrong: 50-char rejected, and true limit observed at 30 ("Should not exceed 30 characters"); 30-char accepted+saved+retrievable (E2092), 31-char rejected. App validation correct and consistent — test-design assumption needs correction, NOT an SUT defect. No BUG filed.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-PIM-003-true-boundary-30-31.png; Expected frozen per process</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -716,14 +921,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Employee Name autocomplete queries /api/v2/pim/employees?nameOrId=Ess, offers suggestion, select+Search returns exactly 1 card (0002 Ess Testuser); Employee Id 0002 likewise returns 1 card</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-PIM-004-exact-name-search.png + TC-PIM-004-autocomplete-suggestion.png</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -733,14 +953,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Employee Id 9999 (no-match) returns 0 cards with "No Records Found" empty state — no stale rows</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-PIM-005-id-no-match-empty-state.png</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -753,11 +988,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -767,14 +997,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>E2091 detail view shows stored creation data; middle-name edit to RegEdit saved ("Successfully Updated") and persists after reload</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>evidence/regression/REG-006-edit-E2091.png</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -787,11 +1032,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -804,11 +1044,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -821,11 +1056,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -838,11 +1068,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -855,11 +1080,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -872,11 +1092,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -889,11 +1104,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -906,11 +1116,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -923,11 +1128,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -937,14 +1137,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ESS Apply Leave renders "No Leave Types with Leave Balance" — submission preconditions (leave type + entitlement/balance for qa_ess) not configured in this cycle; cannot assert submit behaviour</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-LEAVE-002-ess-apply-form.png; precondition: provision leave entitlement then re-execute</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -954,14 +1169,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Same entitlement precondition as TC-LEAVE-001; half-day submit not attemptable</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-LEAVE-002-ess-apply-form.png</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -974,11 +1204,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -991,11 +1216,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1008,11 +1228,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1025,11 +1240,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1042,11 +1252,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1059,11 +1264,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1076,11 +1276,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1093,11 +1288,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1110,11 +1300,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1127,11 +1312,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1141,14 +1321,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ESS punch-in saves ("Successfully Saved") and creates visible attendance record with timestamp in My Records (1 row)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>evidence/regression/REG-010-punched-in.png + REG-010-my-records.png</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1158,14 +1353,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ESS punch-out saves ("Successfully Saved"), completing the in/out cycle the same day</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>evidence/regression/REG-010-punched-out.png</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ubuntu 24.04.5 LTS; Firefox 155.0 (Playwright firefox-1543); OrangeHRM 5.8.1 pinned (5eb278ac); 1920x1080</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1178,11 +1388,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1195,11 +1400,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1212,11 +1412,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1229,11 +1424,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1246,11 +1436,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1263,11 +1448,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1280,11 +1460,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1297,11 +1472,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1314,11 +1484,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1331,11 +1496,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1348,11 +1508,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1365,11 +1520,6 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/06-execution/execution-results.xlsx
+++ b/docs/06-execution/execution-results.xlsx
@@ -830,12 +830,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Employee E2091 (PhaseNine Probe) saved and retrieved by ID search: 1 card E2091 | PhaseNine | Probe</t>
+          <t>E2001 (Aarav Sharma, DOB 1990-01-15 per valid_employee.csv) saved ("Successfully Saved"), found by ID search (1 card), DOB persists after refresh. Conforming rerun 2026-10-03; exploratory E2091 probe retained as supporting evidence.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>evidence/smoke/TC-PIM-001-created-E2091.png; synthetic record, disposable</t>
+          <t>evidence/smoke/TC-PIM-001-E2001-saved.png + TC-PIM-001-E2001-in-list.png + TC-PIM-007-E2001-detail.png</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Empty-required blocked inline ("Required" x2, stays on form); duplicate E2091 blocked ("Employee Id already exists", stays on form); ID search confirms still exactly 1 E2091 record — no silent save, no duplicate</t>
+          <t>Empty-required blocked inline ("Required" x2, stays on form); duplicate E2001 blocked ("Employee Id already exists"); ID search confirms still exactly 1 E2001 record — no silent save, no duplicate. Conforming rerun 2026-10-03.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>evidence/smoke/TC-PIM-002-empty-required.png + TC-PIM-002-duplicate-id.png</t>
+          <t>evidence/smoke/TC-PIM-002-E2001-duplicate.png</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Employee Name autocomplete queries /api/v2/pim/employees?nameOrId=Ess, offers suggestion, select+Search returns exactly 1 card (0002 Ess Testuser); Employee Id 0002 likewise returns 1 card</t>
+          <t>Name autocomplete suggests Aarav; select+Search returns exactly 1 card (E2001 Aarav Sharma); Reset restores full list (6 cards). Conforming rerun 2026-10-03 with search_test_data.csv 'Aarav'.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>evidence/smoke/TC-PIM-004-exact-name-search.png + TC-PIM-004-autocomplete-suggestion.png</t>
+          <t>evidence/smoke/TC-PIM-004-Aarav-search.png</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Employee Id 9999 (no-match) returns 0 cards with "No Records Found" empty state — no stale rows</t>
+          <t>Name query 'ZzzNoMatch' returns 0 cards with 'No Records Found' empty state — no stale rows. Conforming rerun 2026-10-03; free text IS submitted as a filter (earlier select-only theory disproven).</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>evidence/smoke/TC-PIM-005-id-no-match-empty-state.png</t>
+          <t>evidence/smoke/TC-PIM-005-ZzzNoMatch.png</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>E2091 detail view shows stored creation data; middle-name edit to RegEdit saved ("Successfully Updated") and persists after reload</t>
+          <t>E2001 detail shows stored creation data (Aarav Sharma, E2001, DOB 1990-01-15 persists after save+refresh). Conforming rerun 2026-10-03.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>evidence/regression/REG-006-edit-E2091.png</t>
+          <t>evidence/smoke/TC-PIM-007-E2001-detail.png</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
